--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136213276</v>
       </c>
       <c r="B3" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213789</v>
       </c>
       <c r="B4" t="n">
-        <v>98374</v>
+        <v>98375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213342</v>
       </c>
       <c r="B5" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213752</v>
       </c>
       <c r="B6" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136213276</v>
+        <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>101506</v>
+        <v>99340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,41 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällstugan N om , Srm</t>
+          <t>Hällstugan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594262</v>
+        <v>594388</v>
       </c>
       <c r="R3" t="n">
-        <v>6547348</v>
+        <v>6547289</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,39 +881,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Måns Danneman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Måns Danneman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136213276</t>
+          <t>https://artportalen.se/Sighting/136297319</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136213789</v>
+        <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>98375</v>
+        <v>101512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222736</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Majbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Athyrium filix-femina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,14 +939,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällstugan NO om , Srm</t>
+          <t>Hällstugan N om , Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594383</v>
+        <v>594262</v>
       </c>
       <c r="R4" t="n">
-        <v>6547279</v>
+        <v>6547348</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136213789</t>
+          <t>https://artportalen.se/Sighting/136213276</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136213342</v>
+        <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>99573</v>
+        <v>98381</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222812</v>
+        <v>222736</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Majbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Athyrium filix-femina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,14 +1051,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällstugan N om , Srm</t>
+          <t>Hällstugan NO om , Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594262</v>
+        <v>594383</v>
       </c>
       <c r="R5" t="n">
-        <v>6547348</v>
+        <v>6547279</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,16 +1122,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136213342</t>
+          <t>https://artportalen.se/Sighting/136213789</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136213752</v>
+        <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>99579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223358</v>
+        <v>222812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällstugan NO om , Srm</t>
+          <t>Hällstugan N om , Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594383</v>
+        <v>594262</v>
       </c>
       <c r="R6" t="n">
-        <v>6547279</v>
+        <v>6547348</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,6 +1233,118 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136213342</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136213752</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98353</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällstugan NO om , Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594383</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6547279</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136213752</t>
         </is>
@@ -1245,6 +1357,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99340</v>
+        <v>99341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98381</v>
+        <v>98382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99341</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98382</v>
+        <v>98393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98335</v>
+        <v>98348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98393</v>
+        <v>98406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98406</v>
+        <v>98407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99366</v>
+        <v>99379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98407</v>
+        <v>98420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99379</v>
+        <v>99380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
